--- a/spreadsheets/domains/cramps-med_CRAMPS-MED_Workbook.xlsx
+++ b/spreadsheets/domains/cramps-med_CRAMPS-MED_Workbook.xlsx
@@ -2,16 +2,16 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Domain Summary" sheetId="1" r:id="R9e1efd3005594a89"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Preflight Scope" sheetId="2" r:id="Rb8e6e8d4ba7049de"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Preflight Sources" sheetId="3" r:id="Rf39718d02d864f47"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Preflight Rows" sheetId="4" r:id="Re164b08088cc4f36"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gotchas" sheetId="5" r:id="Rfc4ddf0a6f7b4a89"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Full Gate" sheetId="6" r:id="R1882e1c9dcfb4832"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Full Evidence Binder" sheetId="7" r:id="Ra0fee547015e4193"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Import Log" sheetId="8" r:id="R62eeded285e64ee7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Trust Checkpoints" sheetId="9" r:id="Ra512229770fb41e5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reliance Positioning" sheetId="10" r:id="R715ffce097e24490"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Domain Summary" sheetId="1" r:id="R3a2a16a00bbe4ec1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Preflight Scope" sheetId="2" r:id="Rf9075d43c442480f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Preflight Sources" sheetId="3" r:id="R1ca493cbe8694c12"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Preflight Rows" sheetId="4" r:id="Rfb9cbb4c2a1041fd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Failure Modes" sheetId="5" r:id="R706560676d4e4e11"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Full Gate" sheetId="6" r:id="R2935c1ddd78240ad"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Full Evidence Binder" sheetId="7" r:id="R7315282219be4ab9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Import Log" sheetId="8" r:id="R047d825c883843b4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Trust Checkpoints" sheetId="9" r:id="R2918c5abaa184433"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reliance Positioning" sheetId="10" r:id="R94e2569dd6f64bfd"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -250,7 +250,7 @@
     </x:row>
     <x:row r="7">
       <x:c r="A7" t="str">
-        <x:v>Gotchas</x:v>
+        <x:v>Primary failure modes</x:v>
       </x:c>
       <x:c r="B7" t="str">
         <x:v>confounding by indication; differential coding; missing nulls; surveillance bias</x:v>
@@ -1089,7 +1089,7 @@
   <x:sheetData>
     <x:row r="1">
       <x:c r="A1" t="str">
-        <x:v>Gotcha</x:v>
+        <x:v>Failure mode</x:v>
       </x:c>
       <x:c r="B1" t="str">
         <x:v>Status</x:v>
@@ -1255,7 +1255,7 @@
       <x:c r="B6" t="str"/>
       <x:c r="C6" t="str"/>
       <x:c r="D6" t="str">
-        <x:v>raw rows, source trace, extraction confidence, review status, quarantine log</x:v>
+        <x:v>raw signal rows, source trace, extraction confidence, review status, quarantine log</x:v>
       </x:c>
       <x:c r="E6" t="str"/>
     </x:row>
